--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077B28B7-5BBC-5D46-8572-9D33CA08E88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3277D9-F75E-6B48-BF0E-1348659C5CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2600" yWindow="3100" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
@@ -1379,6 +1379,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
         <v>46335</v>
@@ -1403,7 +1406,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
@@ -1428,9 +1431,6 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
         <v>46349</v>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3277D9-F75E-6B48-BF0E-1348659C5CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6233974E-BB59-9149-B9A4-943A72D308A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="3100" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="4820" yWindow="6320" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -137,9 +137,6 @@
     <t>/modules/02-Module.html</t>
   </si>
   <si>
-    <t>/modules/03-Module.html</t>
-  </si>
-  <si>
     <t>/modules/04-Module.html</t>
   </si>
   <si>
@@ -192,6 +189,9 @@
   </si>
   <si>
     <t>No Class - Thanksgiving</t>
+  </si>
+  <si>
+    <t>Project Proposal</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
         <v>17</v>
@@ -1121,7 +1121,7 @@
         <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1140,7 +1140,7 @@
         <v>46265</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>31</v>
@@ -1166,7 +1166,7 @@
         <v>46272</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -1196,7 +1196,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -1218,8 +1218,14 @@
         <f t="shared" si="1"/>
         <v>46286</v>
       </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1239,13 +1245,13 @@
         <v>46293</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
         <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1265,13 +1271,13 @@
         <v>46300</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
         <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1291,13 +1297,13 @@
         <v>46307</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F8" t="s">
         <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1317,13 +1323,13 @@
         <v>46314</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1343,13 +1349,13 @@
         <v>46321</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1369,13 +1375,13 @@
         <v>46328</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1395,13 +1401,13 @@
         <v>46335</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1421,13 +1427,7 @@
         <v>46342</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1444,7 +1444,7 @@
         <v>46349</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1467,7 +1467,7 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G15" t="s">
         <v>29</v>
@@ -1519,7 +1519,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6233974E-BB59-9149-B9A4-943A72D308A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C979880B-804F-1B4C-8281-0E83D34C3132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4820" yWindow="6320" windowWidth="24780" windowHeight="14160" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="7400" yWindow="1320" windowWidth="24780" windowHeight="13780" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Week</t>
   </si>
@@ -192,6 +192,12 @@
   </si>
   <si>
     <t>Project Proposal</t>
+  </si>
+  <si>
+    <t>00-Intro_to_Course</t>
+  </si>
+  <si>
+    <t>WP4_EnN7JXI</t>
   </si>
 </sst>
 </file>
@@ -1148,6 +1154,12 @@
       <c r="G2" t="s">
         <v>18</v>
       </c>
+      <c r="H2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/IS381 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C979880B-804F-1B4C-8281-0E83D34C3132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FE9B0A-AA09-CB44-B6C2-E960071ACB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="1320" windowWidth="24780" windowHeight="13780" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
+    <workbookView xWindow="1220" yWindow="13680" windowWidth="24780" windowHeight="13780" xr2:uid="{BFE2A6F7-E8E8-014E-9460-2468D969C60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Week</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>WP4_EnN7JXI</t>
+  </si>
+  <si>
+    <t>01-Intro_to_Data</t>
+  </si>
+  <si>
+    <t>ofow-rwsCqY</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1192,12 @@
       <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
